--- a/Vantagepoint Project.xlsx
+++ b/Vantagepoint Project.xlsx
@@ -1,42 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JosephDiaz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\edsonperez\hackathon\hackathon-team38-plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E792479-9E13-4754-9991-6ABE70C35C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9F5B59-3C2F-4746-B2F7-15B899930EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E0D904B9-877E-4A20-ABD8-1F4B8565F541}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="95">
   <si>
     <t>Employee Name</t>
   </si>
@@ -44,7 +28,7 @@
     <t>Role</t>
   </si>
   <si>
-    <t>Rate</t>
+    <t>Labor Rate</t>
   </si>
   <si>
     <t>Skills</t>
@@ -59,7 +43,43 @@
     <t>Tenureship</t>
   </si>
   <si>
-    <t>Edison Macabuhay</t>
+    <t>Project Total Budget</t>
+  </si>
+  <si>
+    <t>Project Timeline</t>
+  </si>
+  <si>
+    <t>Allocation %</t>
+  </si>
+  <si>
+    <t>Est. Hours/Week</t>
+  </si>
+  <si>
+    <t>Burden Rate %</t>
+  </si>
+  <si>
+    <t>Fully Burdened Rate</t>
+  </si>
+  <si>
+    <t>Est. Total Labor Cost</t>
+  </si>
+  <si>
+    <t>Billing Rate</t>
+  </si>
+  <si>
+    <t>Target Margin %</t>
+  </si>
+  <si>
+    <t>Revenue Forecast</t>
+  </si>
+  <si>
+    <t>Current Utilization %</t>
+  </si>
+  <si>
+    <t>Risk Level</t>
+  </si>
+  <si>
+    <t>Project Phase</t>
   </si>
   <si>
     <t>Software Engineer</t>
@@ -77,6 +97,21 @@
     <t>6 years</t>
   </si>
   <si>
+    <t>2 years</t>
+  </si>
+  <si>
+    <t>$58.5/hr</t>
+  </si>
+  <si>
+    <t>$70/hr</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
     <t>Maria Santos</t>
   </si>
   <si>
@@ -89,12 +124,18 @@
     <t>Figma, Adobe XD, Prototyping</t>
   </si>
   <si>
-    <t>Project Nova</t>
-  </si>
-  <si>
     <t>5 years</t>
   </si>
   <si>
+    <t>$52.0/hr</t>
+  </si>
+  <si>
+    <t>$62/hr</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
     <t>John Tan</t>
   </si>
   <si>
@@ -107,7 +148,10 @@
     <t>Excel, Power BI, R</t>
   </si>
   <si>
-    <t>Project Orion</t>
+    <t>$49.4/hr</t>
+  </si>
+  <si>
+    <t>$60/hr</t>
   </si>
   <si>
     <t>Priya Sharma</t>
@@ -128,6 +172,21 @@
     <t>8 years</t>
   </si>
   <si>
+    <t>4 years</t>
+  </si>
+  <si>
+    <t>$71.5/hr</t>
+  </si>
+  <si>
+    <t>$85/hr</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Planning</t>
+  </si>
+  <si>
     <t>Ahmed Khan</t>
   </si>
   <si>
@@ -140,13 +199,10 @@
     <t>Selenium, JIRA, Manual Testing</t>
   </si>
   <si>
-    <t>Project Zenith</t>
-  </si>
-  <si>
-    <t>4 years</t>
-  </si>
-  <si>
-    <t>Li Wei</t>
+    <t>$41.6/hr</t>
+  </si>
+  <si>
+    <t>$52/hr</t>
   </si>
   <si>
     <t>DevOps Engineer</t>
@@ -161,24 +217,33 @@
     <t>Project Titan</t>
   </si>
   <si>
-    <t>Sarah Johnson</t>
+    <t>$65.0/hr</t>
+  </si>
+  <si>
+    <t>$78/hr</t>
+  </si>
+  <si>
+    <t>Sam Milby</t>
   </si>
   <si>
     <t>HR Specialist</t>
   </si>
   <si>
-    <t>$35/hr</t>
+    <t>$38.50/hr</t>
   </si>
   <si>
     <t>Recruitment, Payroll, Compliance</t>
   </si>
   <si>
-    <t>Project Support</t>
-  </si>
-  <si>
     <t>9 years</t>
   </si>
   <si>
+    <t>$50.05/hr</t>
+  </si>
+  <si>
+    <t>$58/hr</t>
+  </si>
+  <si>
     <t>David Lee</t>
   </si>
   <si>
@@ -191,12 +256,15 @@
     <t>Requirements, Documentation</t>
   </si>
   <si>
-    <t>Project Apollo</t>
-  </si>
-  <si>
     <t>7 years</t>
   </si>
   <si>
+    <t>$54.6/hr</t>
+  </si>
+  <si>
+    <t>$65/hr</t>
+  </si>
+  <si>
     <t>Emily Wong</t>
   </si>
   <si>
@@ -209,7 +277,10 @@
     <t>React, JavaScript, CSS</t>
   </si>
   <si>
-    <t>Project Vega</t>
+    <t>$57.2/hr</t>
+  </si>
+  <si>
+    <t>$68/hr</t>
   </si>
   <si>
     <t>Carlos Ramirez</t>
@@ -224,17 +295,138 @@
     <t>Java, Spring Boot, APIs</t>
   </si>
   <si>
-    <t>Project Horizon</t>
+    <t>$59.8/hr</t>
+  </si>
+  <si>
+    <t>$72/hr</t>
+  </si>
+  <si>
+    <t>Tony Stark</t>
+  </si>
+  <si>
+    <t>Barry Allen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -247,16 +439,196 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -265,38 +637,203 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -627,264 +1164,695 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41FBFF18-0ECB-4F7E-BE10-DE9330D79410}">
-  <dimension ref="A1:G11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2">
         <v>43905</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
+      <c r="G2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2">
+        <v>10000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2">
+        <v>80</v>
+      </c>
+      <c r="K2">
+        <v>40</v>
+      </c>
+      <c r="L2">
+        <v>30</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2">
+        <v>194688</v>
+      </c>
+      <c r="O2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="Q2">
+        <v>232960</v>
+      </c>
+      <c r="R2">
+        <v>85</v>
+      </c>
+      <c r="S2" t="s">
+        <v>28</v>
+      </c>
+      <c r="T2" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3">
+        <v>44378</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3">
+        <v>10000</v>
+      </c>
+      <c r="I3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3">
+        <v>80</v>
+      </c>
+      <c r="K3">
+        <v>40</v>
+      </c>
+      <c r="L3">
+        <v>30</v>
+      </c>
+      <c r="M3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3">
+        <v>173056</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="P3">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="Q3">
+        <v>206336</v>
+      </c>
+      <c r="R3">
+        <v>78</v>
+      </c>
+      <c r="S3" t="s">
+        <v>37</v>
+      </c>
+      <c r="T3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>43789</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4">
+        <v>10000</v>
+      </c>
+      <c r="I4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4">
+        <v>80</v>
+      </c>
+      <c r="K4">
+        <v>40</v>
+      </c>
+      <c r="L4">
+        <v>30</v>
+      </c>
+      <c r="M4" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4">
+        <v>164403.20000000001</v>
+      </c>
+      <c r="O4" t="s">
+        <v>43</v>
+      </c>
+      <c r="P4">
+        <v>17.7</v>
+      </c>
+      <c r="Q4">
+        <v>199680</v>
+      </c>
+      <c r="R4">
+        <v>72</v>
+      </c>
+      <c r="S4" t="s">
+        <v>37</v>
+      </c>
+      <c r="T4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5">
+        <v>43230</v>
+      </c>
+      <c r="G5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5">
+        <v>5000</v>
+      </c>
+      <c r="I5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5">
+        <v>80</v>
+      </c>
+      <c r="K5">
+        <v>40</v>
+      </c>
+      <c r="L5">
+        <v>30</v>
+      </c>
+      <c r="M5" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5">
+        <v>475904</v>
+      </c>
+      <c r="O5" t="s">
+        <v>52</v>
+      </c>
+      <c r="P5">
+        <v>15.9</v>
+      </c>
+      <c r="Q5">
+        <v>565760</v>
+      </c>
+      <c r="R5">
+        <v>92</v>
+      </c>
+      <c r="S5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6">
+        <v>44586</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>5000</v>
+      </c>
+      <c r="I6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6">
+        <v>80</v>
+      </c>
+      <c r="K6">
+        <v>40</v>
+      </c>
+      <c r="L6">
+        <v>30</v>
+      </c>
+      <c r="M6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6">
+        <v>276889.59999999998</v>
+      </c>
+      <c r="O6" t="s">
+        <v>60</v>
+      </c>
+      <c r="P6">
+        <v>20</v>
+      </c>
+      <c r="Q6">
+        <v>346112</v>
+      </c>
+      <c r="R6">
+        <v>76</v>
+      </c>
+      <c r="S6" t="s">
+        <v>37</v>
+      </c>
+      <c r="T6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7">
+        <v>44086</v>
+      </c>
+      <c r="G7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7">
+        <v>7000</v>
+      </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7">
+        <v>80</v>
+      </c>
+      <c r="K7">
+        <v>40</v>
+      </c>
+      <c r="L7">
+        <v>30</v>
+      </c>
+      <c r="M7" t="s">
+        <v>65</v>
+      </c>
+      <c r="N7">
+        <v>540800</v>
+      </c>
+      <c r="O7" t="s">
+        <v>66</v>
+      </c>
+      <c r="P7">
+        <v>16.7</v>
+      </c>
+      <c r="Q7">
+        <v>648960</v>
+      </c>
+      <c r="R7">
+        <v>84</v>
+      </c>
+      <c r="S7" t="s">
+        <v>28</v>
+      </c>
+      <c r="T7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8">
+        <v>42784</v>
+      </c>
+      <c r="G8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8">
+        <v>7000</v>
+      </c>
+      <c r="I8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8">
+        <v>80</v>
+      </c>
+      <c r="K8">
+        <v>40</v>
+      </c>
+      <c r="L8">
+        <v>30</v>
+      </c>
+      <c r="M8" t="s">
+        <v>72</v>
+      </c>
+      <c r="N8">
+        <v>416416</v>
+      </c>
+      <c r="O8" t="s">
+        <v>73</v>
+      </c>
+      <c r="P8">
+        <v>13.7</v>
+      </c>
+      <c r="Q8">
+        <v>482560</v>
+      </c>
+      <c r="R8">
+        <v>68</v>
+      </c>
+      <c r="S8" t="s">
+        <v>37</v>
+      </c>
+      <c r="T8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>77</v>
+      </c>
+      <c r="E9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9">
+        <v>43560</v>
+      </c>
+      <c r="G9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9">
+        <v>7000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9">
+        <v>80</v>
+      </c>
+      <c r="K9">
+        <v>40</v>
+      </c>
+      <c r="L9">
+        <v>30</v>
+      </c>
+      <c r="M9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N9">
+        <v>454272</v>
+      </c>
+      <c r="O9" t="s">
+        <v>80</v>
+      </c>
+      <c r="P9">
         <v>16</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="3">
-        <v>44378</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
+      <c r="Q9">
+        <v>540800</v>
+      </c>
+      <c r="R9">
+        <v>79</v>
+      </c>
+      <c r="S9" t="s">
+        <v>37</v>
+      </c>
+      <c r="T9" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3">
-        <v>43789</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>12</v>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10">
+        <v>44499</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10">
+        <v>7000</v>
+      </c>
+      <c r="I10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10">
+        <v>80</v>
+      </c>
+      <c r="K10">
+        <v>40</v>
+      </c>
+      <c r="L10">
+        <v>30</v>
+      </c>
+      <c r="M10" t="s">
+        <v>85</v>
+      </c>
+      <c r="N10">
+        <v>475904</v>
+      </c>
+      <c r="O10" t="s">
+        <v>86</v>
+      </c>
+      <c r="P10">
+        <v>15.9</v>
+      </c>
+      <c r="Q10">
+        <v>565760</v>
+      </c>
+      <c r="R10">
+        <v>76</v>
+      </c>
+      <c r="S10" t="s">
+        <v>37</v>
+      </c>
+      <c r="T10" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11">
+        <v>44004</v>
+      </c>
+      <c r="G11" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="H11">
+        <v>7000</v>
+      </c>
+      <c r="I11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11">
+        <v>80</v>
+      </c>
+      <c r="K11">
+        <v>40</v>
+      </c>
+      <c r="L11">
+        <v>30</v>
+      </c>
+      <c r="M11" t="s">
+        <v>91</v>
+      </c>
+      <c r="N11">
+        <v>497536</v>
+      </c>
+      <c r="O11" t="s">
+        <v>92</v>
+      </c>
+      <c r="P11">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="Q11">
+        <v>599040</v>
+      </c>
+      <c r="R11">
+        <v>83</v>
+      </c>
+      <c r="S11" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="3">
-        <v>43230</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="T11" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="3">
-        <v>44586</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="3">
-        <v>44086</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="3">
-        <v>42784</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="3">
-        <v>43560</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="3">
-        <v>44499</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F11" s="3">
-        <v>44004</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
